--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t xml:space="preserve">Auto_Portal_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_004_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_Merchant_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_004_002</t>
   </si>
 </sst>
 </file>
@@ -101,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -129,6 +138,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -186,7 +200,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -196,6 +210,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -276,13 +294,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -324,6 +342,7 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -483,6 +502,46 @@
       </c>
       <c r="F10" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>3333330401</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3333330401</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3333330402</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3333330402</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,6 +40,12 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
+    <t xml:space="preserve">MID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Auto_Portal_001</t>
   </si>
   <si>
@@ -52,55 +58,28 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_Portal_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_001_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_001</t>
+    <t xml:space="preserve">Auto_007_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_Merchant_007</t>
   </si>
   <si>
     <t xml:space="preserve">Admin</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_001_002</t>
+    <t xml:space="preserve">Auto_007_002</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_002_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_002_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_003_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_003_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Portal_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_004_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_004_002</t>
+    <t xml:space="preserve">Auto_008_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_Merchant_008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_008_002</t>
   </si>
 </sst>
 </file>
@@ -110,7 +89,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -138,11 +117,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -213,7 +187,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -294,8 +268,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.77"/>
@@ -322,227 +296,122 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>2222220100</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2222220100</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3333330701</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2222220200</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="2" t="n">
-        <v>2222220200</v>
+        <v>3333330701</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3333330101</v>
+        <v>3333330702</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3333330101</v>
+        <v>3333330702</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3333330102</v>
+        <v>3333330801</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3333330102</v>
+        <v>3333330801</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3333330201</v>
+        <v>3333330802</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3333330201</v>
+        <v>3333330802</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>3333330202</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>3333330202</v>
-      </c>
-      <c r="F7" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>3333330301</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>3333330301</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>3333330302</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3333330302</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2222220300</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>2222220300</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>3333330401</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>3333330401</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>3333330402</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3333330402</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,46 +40,49 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">MID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Portal_001</t>
+    <t xml:space="preserve">automation_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOMATIONTESTMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">automation_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">automation_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO_TEST_MERCHANT_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutomationSuperUser</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
   </si>
   <si>
-    <t xml:space="preserve">A123456</t>
-  </si>
-  <si>
     <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_007_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_007_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_008_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_008_002</t>
   </si>
 </sst>
 </file>
@@ -174,7 +177,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -183,11 +186,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -268,11 +279,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.53"/>
   </cols>
@@ -296,122 +307,207 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>8548594594</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8548594594</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>2222220100</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>2222220100</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>3333330701</v>
-      </c>
-      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>3333330701</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>8548594595</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8548594595</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>3333330702</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3333330702</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="C4" s="3" t="n">
+        <v>8548594590</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>8548594590</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>3333330801</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>3333330801</v>
-      </c>
-      <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>8548594999</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>8548594999</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>8548555446</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>8548555446</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="3" t="n">
+        <v>8758787876</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>8758787876</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>3333330802</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3333330802</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="B8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>8758787877</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8758787877</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>8758787878</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8758787878</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>8758787879</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>8758787879</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,10 +40,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">avinash_hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+    <t xml:space="preserve">automation_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOMATIONTESTMERCHANT</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -52,19 +52,31 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">avinash_hdfc_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-EULA</t>
+    <t xml:space="preserve">automation_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">automation_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO_TEST_MERCHANT_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutomationSuperUser</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
@@ -73,10 +85,7 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
+    <t xml:space="preserve">AutomationSuperUser1</t>
   </si>
 </sst>
 </file>
@@ -184,16 +193,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -273,7 +282,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
@@ -306,40 +315,40 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>8548594594</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8548594594</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="3" t="n">
+        <v>8548594595</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8548594595</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -347,19 +356,19 @@
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="C4" s="3" t="n">
+        <v>8548594590</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>8548594590</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -370,74 +379,102 @@
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
+      <c r="C5" s="3" t="n">
+        <v>8548594999</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>8548594999</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="C6" s="3" t="n">
+        <v>8548555446</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>8548555446</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="3"/>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>8758787876</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>8758787876</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>8758787889</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8758787889</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="3"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">AutomationSuperUser1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutomationSuperUser2</t>
   </si>
 </sst>
 </file>
@@ -180,17 +183,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -283,7 +282,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -311,170 +310,182 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="2" t="n">
         <v>8548594594</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>8548594594</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="n">
         <v>8548594595</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>8548594595</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="2" t="n">
         <v>8548594590</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>8548594590</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="2" t="n">
         <v>8548594999</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>8548594999</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="2" t="n">
         <v>8548555446</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="D6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>8548555446</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="2" t="n">
         <v>8758787876</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>8758787876</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="2" t="n">
         <v>8758787889</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="n">
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>8758787889</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
+    <row r="9" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8758787890</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8758787890</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">AUTOTESTMERCHANT5</t>
   </si>
   <si>
-    <t xml:space="preserve">AutomationSuperUser</t>
+    <t xml:space="preserve">SuperUserOne</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
@@ -85,10 +85,16 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">AutomationSuperUser1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutomationSuperUser2</t>
+    <t xml:space="preserve">SuperUserTwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserThree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserFour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserFive</t>
   </si>
 </sst>
 </file>
@@ -183,13 +189,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -282,7 +292,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -310,182 +320,206 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>8548594594</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>8548594594</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>8548594595</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>8548594595</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>8548594590</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>8548594590</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>8548594999</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>8548594999</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>8548555446</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>8548555446</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>8758787876</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
+      <c r="D7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>8758787876</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>8758787889</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>8758787889</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="C8" s="3" t="n">
+        <v>8758787877</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8758787877</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>8758787890</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>8758787890</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="C9" s="3" t="n">
+        <v>8758787878</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8758787878</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>8758787879</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>8758787879</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3"/>
+      <c r="A11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,10 +40,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">automation_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOMATIONTESTMERCHANT</t>
+    <t xml:space="preserve">auto_user_test_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_Merchant_test_001</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -52,37 +52,19 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">automation_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">automation_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTO_TEST_MERCHANT_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT5</t>
+    <t xml:space="preserve">auto_user_test_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserTest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
   </si>
   <si>
     <t xml:space="preserve">SuperUserOne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
   </si>
   <si>
     <t xml:space="preserve">SuperUserTwo</t>
@@ -189,7 +171,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -198,19 +180,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -291,8 +265,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -324,201 +298,160 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>8548594594</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>8548594594</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="C2" s="2" t="n">
+        <v>6666660801</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>6666660801</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6666660803</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6666660803</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>8548594595</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>8548594595</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>8548594590</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>8548594590</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>6666660802</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6666660802</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8548594999</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>8548594999</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>8758787876</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8758787876</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>8758787877</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>8758787877</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>8758787878</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>8758787878</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>8548555446</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>8548555446</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>8758787879</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>8758787879</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>8758787876</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>8758787876</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>8758787877</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>8758787877</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>8758787878</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>8758787878</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>8758787879</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>8758787879</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>8758787870</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>8758787870</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>20</v>
+      <c r="F9" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,43 +40,34 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
+    <t xml:space="preserve">Test automation b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO TESTMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test automation a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
+    <t xml:space="preserve"> Test automation b</t>
   </si>
 </sst>
 </file>
@@ -171,17 +162,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -269,8 +256,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -302,137 +289,81 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="n">
+        <v>5555554321</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2" t="n">
+        <v>5555554321</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5555543210</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="2" t="n">
+        <v>5555543210</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
+      <c r="E4" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,43 +40,43 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">auto_user_test_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_test_001</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">auto_user_test_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserTest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserOne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserTwo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserThree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserFour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserFive</t>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -171,13 +171,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -266,7 +270,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,19 +302,19 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>6666660801</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>6666660801</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -318,141 +322,117 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>6666660803</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6666660803</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>6666660802</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>6666660802</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8758787876</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8758787876</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>8758787877</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>8758787877</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>13</v>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>8758787878</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>8758787878</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>8758787879</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>8758787879</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,18 +40,24 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Test automation c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
     <t xml:space="preserve">Test automation b</t>
   </si>
   <si>
     <t xml:space="preserve">AUTOTESTMERCHANT7</t>
   </si>
   <si>
-    <t xml:space="preserve">A123456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
     <t xml:space="preserve">AUTO TESTMERCHANT</t>
   </si>
   <si>
@@ -67,7 +73,10 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve"> Test automation b</t>
+    <t xml:space="preserve">Test auto sup acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VineethB</t>
   </si>
 </sst>
 </file>
@@ -256,8 +265,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -293,19 +302,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5555554321</v>
+        <v>5555432100</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5555554321</v>
+        <v>5555432100</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -313,56 +322,96 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5555543210</v>
+        <v>5555554321</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5555543210</v>
+        <v>5555554321</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8891960880</v>
+        <v>5555543210</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8891960880</v>
+        <v>5555543210</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>9731653475</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>9731653475</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>14</v>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>9731545096</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>9731545096</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,43 +40,43 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">auto_user_test_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_Merchant_test_001</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">auto_user_test_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserTest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserOne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserTwo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserThree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserFour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUserFive</t>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -171,13 +171,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -266,7 +270,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,19 +302,19 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>6666660801</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>6666660801</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -318,141 +322,117 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>6666660803</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6666660803</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>6666660802</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>6666660802</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8758787876</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8758787876</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8758787877</v>
+        <v>6789876556</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8758787877</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>13</v>
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8758787878</v>
+        <v>6789343487</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8758787878</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>13</v>
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>8758787879</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>8758787879</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -40,43 +40,43 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
+    <t xml:space="preserve">AUTO TESTMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test automation b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test automation c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test automation a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
+    <t xml:space="preserve">Test auto sup acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VineethB</t>
   </si>
 </sst>
 </file>
@@ -171,17 +171,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -269,8 +265,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,23 +294,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="C2" s="2" t="n">
+        <v>5555543210</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5555543210</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -322,117 +318,101 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5555554321</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5555554321</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5555432100</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5555432100</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F5" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>18</v>
       </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C7" s="2" t="n">
-        <v>6789343487</v>
+        <v>9731545096</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
+        <v>9731545096</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,43 +40,40 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO TESTMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+    <t xml:space="preserve">Sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDEEPTEST_8144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q121212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChethanCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TESTCHETHAN_3087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandeepkumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserFive</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test auto sup acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VineethB</t>
   </si>
 </sst>
 </file>
@@ -171,7 +168,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -181,6 +178,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -265,8 +278,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -301,118 +314,86 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>5555543210</v>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5555543210</v>
+        <v>1232123212</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>9191917171</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="E3" s="5" t="n">
+        <v>9988989809</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="F3" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>9988987089</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="E4" s="2" t="n">
-        <v>5555432100</v>
+        <v>9988987089</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="5" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,28 +40,31 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANDEEPTEST_8144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q121212</t>
+    <t xml:space="preserve">Test automation c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">ChethanCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TESTCHETHAN_3087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandeepkumar</t>
+    <t xml:space="preserve">Test automation b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTO TESTMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test automation a</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
@@ -70,10 +73,10 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">SuperUserFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123456</t>
+    <t xml:space="preserve">Test auto sup acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VineethB</t>
   </si>
 </sst>
 </file>
@@ -168,7 +171,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -178,22 +181,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -278,8 +265,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -307,93 +294,125 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
+      <c r="C2" s="2" t="n">
+        <v>5555432100</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5555432100</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1232123212</v>
-      </c>
-      <c r="F2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>9191917171</v>
+      <c r="C3" s="2" t="n">
+        <v>5555554321</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5555554321</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>9988989809</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="2" t="n">
+        <v>5555543210</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5555543210</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="C5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="D5" s="5" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>9731545096</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>9731545096</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -40,43 +40,43 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Test automation c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Test automation b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTO TESTMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test auto sup acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VineethB</t>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -171,13 +171,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -265,8 +269,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,19 +302,19 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -318,101 +322,117 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="C7" s="2" t="n">
-        <v>9731545096</v>
+        <v>6789343487</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,43 +40,46 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123456</t>
+    <t xml:space="preserve">Sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDEEPTEST_8144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q121212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remotepay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURFY12_30802597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JyTMsFZlfn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMODEV_4516605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q12121212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandeepkumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
   </si>
   <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
+    <t xml:space="preserve">Sandeepkumarrajak</t>
   </si>
 </sst>
 </file>
@@ -171,7 +174,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -180,16 +183,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -269,8 +276,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,141 +305,105 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>1232123212</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>6360953784</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>7736923648</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7736923648</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>9988987089</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="E5" s="2" t="n">
+        <v>9988987089</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>9880132901</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="E6" s="4" t="n">
+        <v>9880132901</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,46 +40,43 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANDEEPTEST_8144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q121212</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Remotepay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MURFY12_30802597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JyTMsFZlfn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMODEV_4516605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q12121212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandeepkumar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandeepkumarrajak</t>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -174,7 +171,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -183,20 +180,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -276,8 +269,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -305,105 +298,141 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1232123212</v>
-      </c>
-      <c r="F2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>6360953784</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>7736923648</v>
-      </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>7736923648</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>9880132901</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>9880132901</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="C7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -40,43 +40,43 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO TESTMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Test automation b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test auto sup acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VineethB</t>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -171,13 +171,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -265,8 +269,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -294,23 +298,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -318,101 +322,117 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="C7" s="2" t="n">
-        <v>9731545096</v>
+        <v>6789343487</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,31 +40,37 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO TESTMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123456</t>
+    <t xml:space="preserve">Sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDEEPTEST_8144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q121212</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Test automation b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation a</t>
+    <t xml:space="preserve">JyTMsFZlfn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMODEV_4516605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q12121212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remotepay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURFY12_30802597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandeepkumar</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
@@ -73,10 +79,10 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Test auto sup acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VineethB</t>
+    <t xml:space="preserve">Sandeepkumarrajak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandeeptest</t>
   </si>
 </sst>
 </file>
@@ -171,7 +177,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -181,11 +187,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -266,7 +280,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -301,123 +315,123 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>5555543210</v>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5555543210</v>
+        <v>1232123212</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>7736923648</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>7736923648</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="E4" s="5" t="n">
+        <v>6360953784</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="F3" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>9988987089</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="E5" s="2" t="n">
+        <v>9988987089</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>9880132901</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="4" t="n">
+        <v>9880132901</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="C7" s="0" t="n">
+        <v>9775822323</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>9775822323</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,49 +40,43 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANDEEPTEST_8144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q121212</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">JyTMsFZlfn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMODEV_4516605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q12121212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remotepay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MURFY12_30802597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandeepkumar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandeepkumarrajak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandeeptest</t>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -177,7 +171,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -186,20 +180,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -279,8 +269,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="12.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -308,130 +298,146 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1232123212</v>
-      </c>
-      <c r="F2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>7736923648</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>7736923648</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>6360953784</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>9880132901</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>9880132901</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>9775822323</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>9775822323</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="C7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,43 +40,49 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123456</t>
+    <t xml:space="preserve">Sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDEEPTEST_8144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q121212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JyTMsFZlfn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMODEV_4516605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q12121212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remotepay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MURFY12_30802597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandeepkumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
   </si>
   <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
+    <t xml:space="preserve">Sandeepkumarrajak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sandeeptest</t>
   </si>
 </sst>
 </file>
@@ -171,7 +177,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -180,16 +186,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -269,8 +279,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="12.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,146 +308,130 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="2" t="n">
+        <v>1232123212</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F3" s="4" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>7736923648</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>7736923648</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="n">
+        <v>6360953784</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>9988987089</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
+      <c r="E5" s="2" t="n">
+        <v>9988987089</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>9880132901</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>9880132901</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="0" t="n">
+        <v>9775822323</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>9775822323</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,43 +40,25 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO TESTMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+    <t xml:space="preserve">Manasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNPAUTOMATIONPHASEI</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test auto sup acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VineethB</t>
   </si>
 </sst>
 </file>
@@ -171,13 +153,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -265,8 +251,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,19 +284,19 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="n">
+        <v>7204644212</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="n">
+        <v>7204644212</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -318,101 +304,29 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5555554321</v>
+        <v>7207207209</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
+        <v>7207207209</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,37 +40,31 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANDEEPTEST_8144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandeep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q121212</t>
+    <t xml:space="preserve">AUTO TESTMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">JyTMsFZlfn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMODEV_4516605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q12121212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remotepay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MURFY12_30802597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandeepkumar</t>
+    <t xml:space="preserve">Test automation b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test automation c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test automation a</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
@@ -79,10 +73,10 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Sandeepkumarrajak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sandeeptest</t>
+    <t xml:space="preserve">Test auto sup acc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VineethB</t>
   </si>
 </sst>
 </file>
@@ -177,7 +171,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -187,19 +181,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -280,7 +266,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="12.09375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -315,123 +301,123 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
+      <c r="C2" s="2" t="n">
+        <v>5555543210</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5555543210</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1232123212</v>
-      </c>
-      <c r="F2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="n">
+        <v>5555554321</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5555554321</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>7736923648</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>7736923648</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="2" t="n">
+        <v>5555432100</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5555432100</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>6360953784</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="C5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8891960880</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>9988987089</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>9731653475</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>9880132901</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>9880132901</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>9775822323</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>9775822323</v>
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>9731545096</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>9731545096</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -42,10 +42,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch24</t>
+    <t xml:space="preserve">Auto_test_user13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch13</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -54,6 +54,12 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
+    <t xml:space="preserve">Auto_test_user14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acquirer Code</t>
   </si>
   <si>
@@ -73,6 +79,39 @@
   </si>
   <si>
     <t xml:space="preserve">AXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
   <si>
     <t xml:space="preserve">YES</t>
@@ -109,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -137,6 +176,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -194,7 +238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -211,11 +255,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -297,7 +337,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -333,25 +373,37 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188815</v>
+        <v>9300178815</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188815</v>
+        <v>9300178815</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>9300178816</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>9300178816</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -370,74 +422,60 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="B1" s="0" t="s">
         <v>13</v>
       </c>
+      <c r="C1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>15</v>
+      <c r="A2" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A3" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
+      <c r="B3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -455,77 +493,225 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="3" t="n">
-        <v>1</v>
+      <c r="C1" s="2" t="n">
+        <v>9660867345</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
+    </row>
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9660867344</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>9660867300</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
+      <c r="C4" s="2" t="n">
+        <v>7897485874</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
+      <c r="B12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -9,6 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,10 +42,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO TESTMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+    <t xml:space="preserve">Auto_test_user13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch13</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -52,31 +54,91 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Test automation b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
+    <t xml:space="preserve">Auto_test_user14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquirer Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSM Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Test auto sup acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VineethB</t>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB</t>
   </si>
 </sst>
 </file>
@@ -86,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -114,6 +176,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -171,7 +238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -185,6 +252,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -265,7 +336,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
@@ -294,7 +365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -302,13 +373,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="D2" s="3" t="s">
+        <v>9300178815</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5555543210</v>
+        <v>9300178815</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -322,96 +393,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>9300178816</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5555554321</v>
+        <v>9300178816</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -423,4 +414,313 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.89"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -41,10 +42,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch15</t>
+    <t xml:space="preserve">Auto_test_user13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch13</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -53,10 +54,10 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch16</t>
+    <t xml:space="preserve">Auto_test_user14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch14</t>
   </si>
   <si>
     <t xml:space="preserve">Acquirer Code</t>
@@ -71,34 +72,67 @@
     <t xml:space="preserve">HSM Name</t>
   </si>
   <si>
+    <t xml:space="preserve">HDFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">KOTAK</t>
   </si>
   <si>
     <t xml:space="preserve">KOTAK_ATOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDFC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICICI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATOS_TLE</t>
   </si>
   <si>
     <t xml:space="preserve">AIRP</t>
@@ -114,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -142,6 +176,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -199,7 +238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -216,11 +255,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -302,7 +337,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -330,7 +365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -338,19 +373,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9410178815</v>
+        <v>9300178815</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9410178815</v>
+        <v>9300178815</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -358,13 +393,13 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>9410178816</v>
+        <v>9300178816</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9410178816</v>
+        <v>9300178816</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>9</v>
@@ -386,145 +421,298 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="0" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
+      <c r="B2" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9660867344</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B12" s="0" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B15" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="B18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -10,7 +10,6 @@
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -79,66 +78,6 @@
   </si>
   <si>
     <t xml:space="preserve">AXIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICICI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATOS_TLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOTAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOTAK_ATOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB</t>
   </si>
 </sst>
 </file>
@@ -148,7 +87,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -176,11 +115,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -255,7 +189,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -337,7 +271,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -422,13 +356,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -476,243 +410,6 @@
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>17</v>
-      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -41,10 +41,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch13</t>
+    <t xml:space="preserve">Auto_test_user15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch15</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch14</t>
+    <t xml:space="preserve">Auto_test_user16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch16</t>
   </si>
   <si>
     <t xml:space="preserve">Acquirer Code</t>
@@ -71,13 +71,40 @@
     <t xml:space="preserve">HSM Name</t>
   </si>
   <si>
+    <t xml:space="preserve">KOTAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE</t>
+  </si>
+  <si>
     <t xml:space="preserve">HDFC</t>
   </si>
   <si>
-    <t xml:space="preserve">NONE</t>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC</t>
   </si>
   <si>
     <t xml:space="preserve">AXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB</t>
   </si>
 </sst>
 </file>
@@ -172,7 +199,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -186,6 +213,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -271,7 +302,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -299,7 +330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -307,19 +338,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9300178815</v>
+        <v>9410178815</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9300178815</v>
+        <v>9410178815</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -327,13 +358,13 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>9300178816</v>
+        <v>9410178816</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9300178816</v>
+        <v>9410178816</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>9</v>
@@ -355,8 +386,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -366,50 +397,134 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -10,7 +10,6 @@
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -42,10 +41,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch13</t>
+    <t xml:space="preserve">Auto_test_user17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch17</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -54,12 +53,6 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Acquirer Code</t>
   </si>
   <si>
@@ -79,39 +72,6 @@
   </si>
   <si>
     <t xml:space="preserve">AXIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
   <si>
     <t xml:space="preserve">YES</t>
@@ -148,7 +108,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -176,11 +136,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -238,7 +193,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -255,7 +210,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -337,7 +296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -365,7 +324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -373,37 +332,25 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9300178815</v>
+        <v>9510188815</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9300178815</v>
+        <v>9510188815</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>9300178816</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>9300178816</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -422,297 +369,144 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="0" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>17</v>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>17</v>
-      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -41,10 +41,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch17</t>
+    <t xml:space="preserve">Auto_test_user18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch18</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -296,7 +296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -324,7 +324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -332,13 +332,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9510188815</v>
+        <v>9511188815</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9510188815</v>
+        <v>9511188815</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -369,7 +369,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -41,10 +42,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch18</t>
+    <t xml:space="preserve">Auto_test_user24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch24</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -296,7 +297,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -332,13 +333,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9511188815</v>
+        <v>8921188815</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9511188815</v>
+        <v>8921188815</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -369,7 +370,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -434,79 +435,98 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -297,7 +297,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -370,7 +370,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -456,7 +456,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Manasa</t>
+    <t xml:space="preserve">AVI-EULA</t>
   </si>
   <si>
     <t xml:space="preserve">Ezetap</t>
@@ -52,13 +52,31 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">anika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNPAUTOMATIONPHASEI</t>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -251,8 +269,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -280,7 +298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -288,13 +306,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7204644212</v>
+        <v>9660867345</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7204644212</v>
+        <v>9660867345</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
@@ -304,29 +322,117 @@
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>7207207209</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>7207207209</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,12 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="41">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -66,15 +65,48 @@
     <t xml:space="preserve">HSM Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI(psp) Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key for UPI</t>
+  </si>
+  <si>
     <t xml:space="preserve">HDFC</t>
   </si>
   <si>
     <t xml:space="preserve">NONE</t>
   </si>
   <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57c3f7c3b0d8dc0be189ec63f68fce42</t>
+  </si>
+  <si>
     <t xml:space="preserve">AXIS</t>
   </si>
   <si>
+    <t xml:space="preserve">AXIS_DIRECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
     <t xml:space="preserve">YES</t>
   </si>
   <si>
@@ -87,27 +119,40 @@
     <t xml:space="preserve">FDC</t>
   </si>
   <si>
+    <t xml:space="preserve">FDC_ICICI</t>
+  </si>
+  <si>
     <t xml:space="preserve">ATOS_TLE</t>
   </si>
   <si>
+    <t xml:space="preserve">AXIS_TLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">KOTAK</t>
   </si>
   <si>
     <t xml:space="preserve">KOTAK_ATOS</t>
   </si>
   <si>
+    <t xml:space="preserve">KOTAK_WL</t>
+  </si>
+  <si>
     <t xml:space="preserve">AIRP</t>
   </si>
   <si>
     <t xml:space="preserve">APB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal Dependant</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -194,7 +239,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -212,6 +257,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -297,7 +350,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -369,14 +422,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AA16"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -392,143 +450,297 @@
       <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="E1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA8" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA9" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J16" s="7"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+      <formula1>AcquisitionDetails!$AA$9:$AA$9</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -41,10 +41,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch24</t>
+    <t xml:space="preserve">Auto_test_user25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch25</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -53,6 +53,12 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
+    <t xml:space="preserve">Auto_test_user26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acquirer Code</t>
   </si>
   <si>
@@ -83,6 +89,9 @@
     <t xml:space="preserve">Key for UPI</t>
   </si>
   <si>
+    <t xml:space="preserve">virtual MID Required</t>
+  </si>
+  <si>
     <t xml:space="preserve">HDFC</t>
   </si>
   <si>
@@ -95,6 +104,9 @@
     <t xml:space="preserve">57c3f7c3b0d8dc0be189ec63f68fce42</t>
   </si>
   <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
     <t xml:space="preserve">AXIS</t>
   </si>
   <si>
@@ -102,9 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">False</t>
   </si>
   <si>
     <t xml:space="preserve">YES</t>
@@ -350,7 +359,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -386,25 +395,37 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188815</v>
+        <v>8921188816</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188815</v>
+        <v>8921188816</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>8921188916</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8921188916</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -423,7 +444,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -431,97 +452,104 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>27</v>
@@ -530,30 +558,33 @@
         <v>27</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>27</v>
@@ -562,62 +593,68 @@
         <v>27</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>26</v>
+      <c r="K5" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>27</v>
@@ -626,30 +663,33 @@
         <v>27</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>27</v>
@@ -658,30 +698,33 @@
         <v>27</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>27</v>
@@ -690,33 +733,36 @@
         <v>27</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="AA8" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>27</v>
@@ -725,10 +771,13 @@
         <v>27</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -736,7 +785,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9 K2:K9" type="list">
       <formula1>AcquisitionDetails!$AA$9:$AA$9</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="42">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -41,22 +41,16 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch25</t>
+    <t xml:space="preserve">Auto_test_user27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch27</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_user26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch26</t>
   </si>
   <si>
     <t xml:space="preserve">Acquirer Code</t>
@@ -395,37 +389,25 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188816</v>
+        <v>8921188817</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188816</v>
+        <v>8921188817</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>8921188916</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>8921188916</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -461,323 +443,323 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="K2" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA8" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA8" s="0" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -41,10 +41,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch27</t>
+    <t xml:space="preserve">Auto_test_user28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch28</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -353,7 +353,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -389,13 +389,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188817</v>
+        <v>8921188818</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188817</v>
+        <v>8921188818</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -426,7 +426,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -41,10 +41,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch28</t>
+    <t xml:space="preserve">Auto_test_user29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch29</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -353,7 +353,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -389,13 +389,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188818</v>
+        <v>8921188819</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188818</v>
+        <v>8921188819</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -426,7 +426,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -528,7 +528,7 @@
         <v>27</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>26</v>
@@ -703,7 +703,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>40</v>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,11 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="RemotepaySettings" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="PgDetails" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="90">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -41,10 +43,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch29</t>
+    <t xml:space="preserve">Auto_test_user31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch31</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -147,6 +149,150 @@
   </si>
   <si>
     <t xml:space="preserve">Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cnpTxnTimeoutDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximumPayAttemptsAllowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxUpiAttemptInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePayExpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnAndroidDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnNonAndroidDevices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabledInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hash Algo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mle Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cnp Cardpay Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Label Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYBERSOURCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DV+y0pRK1jhkpBipZ+YtM06XqQGOi1SDwsmOY/K4wqo=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8bf3bb8f-eb7c-45d2-b227-bf779907d017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2989436385NXGVOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4053377546CSKYIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T297100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIRST_amount_0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470|TPSL Bank::</t>
   </si>
 </sst>
 </file>
@@ -157,7 +303,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -185,6 +331,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -242,7 +393,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -272,6 +423,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -353,7 +512,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -389,13 +548,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188819</v>
+        <v>8921188821</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188819</v>
+        <v>8921188821</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -426,7 +585,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -525,13 +684,13 @@
         <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>25</v>
@@ -601,7 +760,7 @@
         <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>25</v>
@@ -780,4 +939,428 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.58"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.77"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="94">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -43,10 +43,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch31</t>
+    <t xml:space="preserve">Auto_test_user32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch32</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -88,6 +88,12 @@
     <t xml:space="preserve">virtual MID Required</t>
   </si>
   <si>
+    <t xml:space="preserve">BQR settings required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI settings required</t>
+  </si>
+  <si>
     <t xml:space="preserve">HDFC</t>
   </si>
   <si>
@@ -103,6 +109,9 @@
     <t xml:space="preserve">False</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">AXIS</t>
   </si>
   <si>
@@ -110,6 +119,9 @@
   </si>
   <si>
     <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">YES</t>
@@ -303,7 +315,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -331,11 +343,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -393,7 +400,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -428,10 +435,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -512,7 +515,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -548,13 +551,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188821</v>
+        <v>8921188822</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188821</v>
+        <v>8921188822</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -585,7 +588,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -597,6 +600,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.74"/>
   </cols>
   <sheetData>
@@ -634,291 +639,345 @@
       <c r="K1" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="AA8" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="L9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA9" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA9" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -947,9 +1006,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -957,229 +1016,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1199,111 +1258,111 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I2" s="9" t="n">
+      <c r="F2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>82</v>
+      <c r="J2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="n">
@@ -1312,42 +1371,42 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>87</v>
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="9" t="s">
-        <v>88</v>
+      <c r="G3" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>82</v>
+      <c r="J3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="n">

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,7 +41,7 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVI-EULA</t>
+    <t xml:space="preserve">Manasa</t>
   </si>
   <si>
     <t xml:space="preserve">Ezetap</t>
@@ -52,31 +53,13 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+    <t xml:space="preserve">anika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNPAUTOMATIONPHASEI</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -269,8 +252,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -298,7 +281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -306,133 +289,69 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9660867345</v>
+        <v>7204644212</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>9660867345</v>
+        <v>7204644212</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>9660867344</v>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>7207207209</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>9660867344</v>
+      <c r="E3" s="2" t="n">
+        <v>7207207209</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -443,4 +362,43 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>7207207209</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>7207207209</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -41,7 +40,7 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Manasa</t>
+    <t xml:space="preserve">AVI-EULA</t>
   </si>
   <si>
     <t xml:space="preserve">Ezetap</t>
@@ -53,13 +52,31 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">anika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNPAUTOMATIONPHASEI</t>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_7</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinash-hdfc-two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avinashthree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTEST2_355</t>
   </si>
 </sst>
 </file>
@@ -252,8 +269,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -281,7 +298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -289,69 +306,133 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7204644212</v>
+        <v>9660867345</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7204644212</v>
+        <v>9660867345</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>7207207209</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>7207207209</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7897485874</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6789876556</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6789343487</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -362,43 +443,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="2" t="n">
-        <v>7207207209</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>7207207209</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -43,10 +43,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch32</t>
+    <t xml:space="preserve">Auto_test_user41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch41</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -515,7 +515,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -551,13 +551,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8921188822</v>
+        <v>8922188831</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8921188822</v>
+        <v>8922188831</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -588,7 +588,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -763,7 +763,7 @@
         <v>27</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>28</v>
@@ -804,7 +804,7 @@
         <v>27</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>28</v>
@@ -845,7 +845,7 @@
         <v>27</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>28</v>
@@ -886,7 +886,7 @@
         <v>27</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>28</v>
@@ -971,7 +971,7 @@
         <v>25</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>28</v>
@@ -1006,7 +1006,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1258,7 +1258,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="96">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -43,10 +43,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch41</t>
+    <t xml:space="preserve">Auto_test_user45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch45</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">UPI Terminal Dependant</t>
   </si>
   <si>
-    <t xml:space="preserve">Key for UPI</t>
+    <t xml:space="preserve">App Key for UPI</t>
   </si>
   <si>
     <t xml:space="preserve">virtual MID Required</t>
@@ -94,6 +94,9 @@
     <t xml:space="preserve">UPI settings required</t>
   </si>
   <si>
+    <t xml:space="preserve">Enc Key for UPI</t>
+  </si>
+  <si>
     <t xml:space="preserve">HDFC</t>
   </si>
   <si>
@@ -112,15 +115,15 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AXIS</t>
   </si>
   <si>
     <t xml:space="preserve">AXIS_DIRECT</t>
   </si>
   <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
@@ -160,7 +163,10 @@
     <t xml:space="preserve">APB</t>
   </si>
   <si>
-    <t xml:space="preserve">Terminal Dependant</t>
+    <t xml:space="preserve">4ba841d6-c012-4d19-ab49-2ee74366171p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7f617238-fb82-4b</t>
   </si>
   <si>
     <t xml:space="preserve">Value</t>
@@ -425,11 +431,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -515,7 +521,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -551,13 +557,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922188831</v>
+        <v>8922188835</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922188831</v>
+        <v>8922188835</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -587,8 +593,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA16"/>
-  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AA53"/>
+  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -598,10 +604,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.74"/>
   </cols>
   <sheetData>
@@ -645,348 +652,379 @@
       <c r="M1" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="N1" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA8" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA9" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J16" s="7"/>
+      <c r="N9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA53" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9 K2:K9" type="list">
-      <formula1>AcquisitionDetails!$AA$9:$AA$9</formula1>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1006,7 +1044,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1016,229 +1054,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>10786</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1275,60 +1313,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>120000000008131</v>
@@ -1340,29 +1378,29 @@
         <v>120000000008131</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="n">
@@ -1371,42 +1409,42 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="n">

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -43,10 +43,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch45</t>
+    <t xml:space="preserve">Auto_test_user46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch46</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -521,7 +521,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.31640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -557,13 +557,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922188835</v>
+        <v>8922188836</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922188835</v>
+        <v>8922188836</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -594,7 +594,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="11.94140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1044,7 +1044,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1296,7 +1296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -43,10 +43,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch46</t>
+    <t xml:space="preserve">Auto_test_user49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch49</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -521,7 +521,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.31640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -557,13 +557,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922188836</v>
+        <v>8922188839</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922188836</v>
+        <v>8922188839</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -594,7 +594,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="11.9765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1044,7 +1044,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1296,7 +1296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -12,6 +12,7 @@
     <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="RemotepaySettings" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="PgDetails" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="105">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -43,10 +44,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch49</t>
+    <t xml:space="preserve">Auto_test_user50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch50</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -311,6 +312,33 @@
   </si>
   <si>
     <t xml:space="preserve">470|TPSL Bank::</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qrCodesEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHARAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePaymentEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ctlsEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refundEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onlineRefundEnabled</t>
   </si>
 </sst>
 </file>
@@ -406,7 +434,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -441,6 +469,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -521,7 +553,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -557,13 +589,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922188839</v>
+        <v>8922188840</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922188839</v>
+        <v>8922188840</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -594,7 +626,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1044,7 +1076,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1296,7 +1328,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="11.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1460,4 +1492,152 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="9"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="9"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="9"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="9"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="9"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="9"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="9"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="9"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="106">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch50</t>
+    <t xml:space="preserve">Auto_test_user57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch57</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t xml:space="preserve">Transaction Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNP Terminal Dependant</t>
   </si>
   <si>
     <t xml:space="preserve">CYBERSOURCE</t>
@@ -553,7 +556,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -589,13 +592,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922188840</v>
+        <v>8922188847</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922188840</v>
+        <v>8922188847</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -626,7 +629,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1076,7 +1079,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1327,8 +1330,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1341,6 +1344,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1392,13 +1396,16 @@
       <c r="P1" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="Q1" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>120000000008131</v>
@@ -1410,80 +1417,92 @@
         <v>120000000008131</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3" t="n">
         <v>-1</v>
       </c>
+      <c r="Q2" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="n">
         <v>-1</v>
       </c>
+      <c r="Q3" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1500,7 +1519,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1508,15 +1527,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>64</v>
@@ -1524,15 +1543,15 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>64</v>
@@ -1540,7 +1559,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>64</v>
@@ -1548,7 +1567,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>64</v>
@@ -1556,7 +1575,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>64</v>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch57</t>
+    <t xml:space="preserve">Auto_test_user58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch58</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -556,7 +556,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -592,13 +592,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922188847</v>
+        <v>8922188848</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922188847</v>
+        <v>8922188848</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -629,7 +629,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.2265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1079,7 +1079,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1331,7 +1331,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1519,7 +1519,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch58</t>
+    <t xml:space="preserve">Auto_test_user59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch59</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -556,7 +556,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -592,13 +592,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922188848</v>
+        <v>8922188849</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922188848</v>
+        <v>8922188849</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
@@ -629,7 +629,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.25390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1079,7 +1079,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1331,7 +1331,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1519,7 +1519,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -9,6 +9,10 @@
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="RemotepaySettings" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="PgDetails" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="106">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,10 +44,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">avinash-hdfc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_7</t>
+    <t xml:space="preserve">Auto_test_user61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch61</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -52,33 +56,301 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">avinash-hdfc-two</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">avinashthree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTEST2_355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">swampos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
+    <t xml:space="preserve">Acquirer Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSM Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI(psp) Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App Key for UPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">virtual MID Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR settings required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI settings required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enc Key for UPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57c3f7c3b0d8dc0be189ec63f68fce42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS_DIRECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_WL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4ba841d6-c012-4d19-ab49-2ee74366171p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7f617238-fb82-4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cnpTxnTimeoutDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximumPayAttemptsAllowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxUpiAttemptInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePayExpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnAndroidDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnNonAndroidDevices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabledInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hash Algo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mle Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cnp Cardpay Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Label Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNP Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYBERSOURCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DV+y0pRK1jhkpBipZ+YtM06XqQGOi1SDwsmOY/K4wqo=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8bf3bb8f-eb7c-45d2-b227-bf779907d017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2989436385NXGVOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4053377546CSKYIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T297100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIRST_amount_0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470|TPSL Bank::</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qrCodesEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHARAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePaymentEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ctlsEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refundEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onlineRefundEnabled</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -165,7 +437,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -174,15 +446,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -263,8 +555,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -299,86 +591,90 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="n">
+        <v>3852694001</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>7897485874</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2" t="n">
+        <v>3852694001</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6789876556</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>6789343487</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8928783323</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>8928783323</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -389,4 +685,1042 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AA53"/>
+  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA53" s="7"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.23"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="9"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="9"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="9"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="9"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="9"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="9"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="9"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="9"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="9"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="111">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -44,13 +44,28 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto_test_user61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch61</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-test-user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch47</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
@@ -437,13 +452,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -556,7 +575,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -588,93 +607,129 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>3852694001</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>3852694001</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>8922188837</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8922188837</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -693,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -712,409 +767,409 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="J1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="D2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="L9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="M9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J15" s="6"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AA52" s="7"/>
+      <c r="AA52" s="8"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AA53" s="7"/>
+      <c r="AA53" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1143,239 +1198,239 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="C2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="3" t="n">
+      <c r="E2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>57</v>
+      <c r="G2" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="E3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>57</v>
+      <c r="G3" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="A4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>57</v>
+      <c r="G4" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>57</v>
+      <c r="G5" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="F6" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="E7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="3" t="n">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="n">
+      <c r="E10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>57</v>
+      <c r="G10" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1450,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1412,152 +1467,152 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>83</v>
       </c>
+      <c r="M1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="F2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3" t="n">
+      <c r="J2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" s="5" t="s">
-        <v>26</v>
+      <c r="Q2" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3" t="n">
+      <c r="M3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="Q3" s="5" t="s">
-        <v>26</v>
+      <c r="Q3" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1583,136 +1638,136 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>98</v>
+      <c r="A1" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>64</v>
+      <c r="A2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>101</v>
+      <c r="A3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>64</v>
+      <c r="A4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>64</v>
+      <c r="A5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>64</v>
+      <c r="A6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>64</v>
+      <c r="A7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="9"/>
+      <c r="B8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9"/>
+      <c r="B9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9"/>
+      <c r="B10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9"/>
+      <c r="B11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9"/>
+      <c r="B12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9"/>
+      <c r="B13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9"/>
+      <c r="B14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9"/>
+      <c r="B15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9"/>
+      <c r="B16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9"/>
+      <c r="B17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9"/>
+      <c r="B18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="9"/>
+      <c r="B19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9"/>
+      <c r="B20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9"/>
+      <c r="B21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="9"/>
+      <c r="B22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="9"/>
+      <c r="B23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9"/>
+      <c r="B24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="9"/>
+      <c r="B25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="9"/>
+      <c r="B26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="9"/>
+      <c r="B27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="9"/>
+      <c r="B28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="9"/>
+      <c r="B29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="9"/>
+      <c r="B30" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="121">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -44,31 +44,125 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123456</t>
+    <t xml:space="preserve">EzeAutoSuperUser-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123457</t>
   </si>
   <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avinash-one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-test-user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch47</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">EzeAuto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SuperUser-2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">EzeAuto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SuperUser-3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">EzeAuto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SuperUser-4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">EzeAuto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SuperUser-5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAuto_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMERCHANT_1</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAuto_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMERCHANT_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAuto_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMERCHANT_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAuto_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMERCHANT_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAuto_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMERCHANT_5</t>
   </si>
   <si>
     <t xml:space="preserve">Acquirer Code</t>
@@ -367,7 +461,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -395,6 +489,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -452,7 +551,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -461,16 +560,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -575,7 +678,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="12.796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -603,138 +706,210 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="n">
+        <v>6758787866</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>9660867345</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2" t="n">
+        <v>6758787866</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="2" t="n">
+        <v>6758787867</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="2" t="n">
+        <v>6758787867</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="2" t="n">
+        <v>6758787868</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>9660867300</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="2" t="n">
+        <v>6758787868</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>6758787869</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6758787869</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>8922188837</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6758787860</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>8922188837</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E6" s="2" t="n">
+        <v>6758787860</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6548594513</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6548594513</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>6548594515</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6548594515</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>6548594510</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6548594510</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>6548594919</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>6548594919</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>6548555416</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>6548555416</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -748,7 +923,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.43359375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.3359375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -767,424 +942,424 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>28</v>
       </c>
+      <c r="E1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>35</v>
+      <c r="D2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="A3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>35</v>
+      <c r="D3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="D5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="M9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J15" s="7"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AA52" s="8"/>
+      <c r="AA52" s="9"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AA53" s="8"/>
+      <c r="AA53" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1198,245 +1373,245 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>58</v>
+      <c r="B1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="C2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="E2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>62</v>
+      <c r="G2" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="4" t="n">
+      <c r="A3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="C3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="E3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>62</v>
+      <c r="G3" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="4" t="n">
+      <c r="A4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="C4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="E4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>62</v>
+      <c r="G4" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="4" t="n">
+      <c r="A5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="E5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>62</v>
+      <c r="G5" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="4" t="n">
+      <c r="A6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>62</v>
+      <c r="G6" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="4" t="n">
+      <c r="A7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>62</v>
+      <c r="G7" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="E8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>62</v>
+      <c r="G8" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>62</v>
+      <c r="G9" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1450,7 +1625,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1467,164 +1642,164 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="F2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="n">
+      <c r="J2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>31</v>
+      <c r="Q2" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="n">
+      <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4" t="n">
+      <c r="J3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>31</v>
+      <c r="Q3" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1638,141 +1813,141 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>103</v>
+      <c r="A1" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>69</v>
+      <c r="A2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>106</v>
+      <c r="A3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>69</v>
+      <c r="A4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>69</v>
+      <c r="A5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>69</v>
+      <c r="A6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>69</v>
+      <c r="A7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10"/>
+      <c r="B8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10"/>
+      <c r="B9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10"/>
+      <c r="B10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10"/>
+      <c r="B11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
+      <c r="B12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10"/>
+      <c r="B13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10"/>
+      <c r="B14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10"/>
+      <c r="B15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10"/>
+      <c r="B16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10"/>
+      <c r="B17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10"/>
+      <c r="B18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10"/>
+      <c r="B19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10"/>
+      <c r="B20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
+      <c r="B21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10"/>
+      <c r="B22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10"/>
+      <c r="B23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10"/>
+      <c r="B24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10"/>
+      <c r="B25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10"/>
+      <c r="B26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10"/>
+      <c r="B27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10"/>
+      <c r="B28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10"/>
+      <c r="B29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10"/>
+      <c r="B30" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -575,7 +575,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="12.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -663,7 +663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -748,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.43359375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1198,7 +1198,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1450,7 +1450,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1638,7 +1638,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -9,6 +9,10 @@
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="AcquisitionDetails" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="RemotepaySettings" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="PgDetails" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="110">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,51 +44,325 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTO TESTMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT6</t>
+    <t xml:space="preserve">AVISUPERUSER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUSER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVINASHTESTUPI_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123457</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Test automation b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test automation a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test auto sup acc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VineethB</t>
+    <t xml:space="preserve">Acquirer Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSM Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI(psp) Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App Key for UPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">virtual MID Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR settings required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI settings required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enc Key for UPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57c3f7c3b0d8dc0be189ec63f68fce42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS_DIRECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_WL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4ba841d6-c012-4d19-ab49-2ee74366171p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7f617238-fb82-4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cnpTxnTimeoutDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximumPayAttemptsAllowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxUpiAttemptInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePayExpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnAndroidDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnNonAndroidDevices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabledInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hash Algo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mle Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cnp Cardpay Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Label Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNP Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYBERSOURCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DV+y0pRK1jhkpBipZ+YtM06XqQGOi1SDwsmOY/K4wqo=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8bf3bb8f-eb7c-45d2-b227-bf779907d017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2989436385NXGVOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4053377546CSKYIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T297100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIRST_amount_0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470|TPSL Bank::</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qrCodesEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHARAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePaymentEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ctlsEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refundEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onlineRefundEnabled</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -171,7 +449,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -180,11 +458,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -266,7 +572,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -294,23 +600,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>5555543210</v>
+      <c r="C2" s="3" t="n">
+        <v>9660867399</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>5555543210</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="n">
+        <v>9660867399</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -322,97 +628,49 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5555554321</v>
+        <v>7897485878</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5555554321</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
+        <v>7897485878</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9731653475</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9731545096</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -423,4 +681,1042 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AA53"/>
+  <sheetFormatPr defaultColWidth="12.37109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA52" s="8"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AA53" s="8"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="12.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="12.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.23"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+      <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="10"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="111">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVISUPERUSER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -56,13 +56,16 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">AVINASHTESTUSER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVINASHTESTUPI_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123457</t>
+    <t xml:space="preserve">Avin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avinash-one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-test-user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch47</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
@@ -572,7 +575,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -600,7 +603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -608,53 +611,77 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9660867399</v>
-      </c>
-      <c r="D2" s="3" t="s">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>9660867399</v>
+        <v>9660867345</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9660867344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>7897485878</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9660867300</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>7897485878</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
+      <c r="C5" s="2" t="n">
+        <v>8922188837</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8922188837</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
@@ -689,7 +716,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.37109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -709,398 +736,398 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="K3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="M4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="M6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="M7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="K9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1139,7 +1166,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1149,229 +1176,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="C9" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1418,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1409,63 +1436,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>120000000008131</v>
@@ -1477,83 +1504,83 @@
         <v>120000000008131</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1606,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1587,58 +1614,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -13,6 +13,7 @@
     <sheet name="RemotepaySettings" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="PgDetails" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="ConfigDetails" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="120">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -357,6 +358,33 @@
   </si>
   <si>
     <t xml:space="preserve">onlineRefundEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConfigMerchant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOACONFIGMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRTELULB_540943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWMCCONFIGMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHOPALMUNICIPALFDC</t>
   </si>
 </sst>
 </file>
@@ -452,7 +480,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -495,6 +523,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -575,7 +607,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.83203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -716,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.47265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1166,7 +1198,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1418,7 +1450,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1606,7 +1638,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1736,6 +1768,100 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="10"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>7207207205</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>7207207202</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>7207207203</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>7207207206</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -607,7 +607,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="12.83203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.8671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -748,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.47265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1198,7 +1198,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1450,7 +1450,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1638,7 +1638,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1786,7 +1786,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.87"/>
@@ -1815,7 +1815,7 @@
         <v>113</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>7207207205</v>
+        <v>7207207201</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>8</v>
@@ -1857,7 +1857,7 @@
         <v>119</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>7207207206</v>
+        <v>7207207205</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>8</v>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -13,7 +13,6 @@
     <sheet name="RemotepaySettings" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="PgDetails" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="ConfigDetails" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="121">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -45,27 +44,63 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Manasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123456</t>
+    <t xml:space="preserve">EzeAutoSuperUser-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZETAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123457</t>
   </si>
   <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">AutotestuserSwati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch59</t>
+    <t xml:space="preserve">EzeAutoSuperUser-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAutoSuperUser-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAutoSuperUser-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAutoSuperUser-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAutomation_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMAMERCHANT_11</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
+    <t xml:space="preserve">EzeAutomation_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMAMERCHANT_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAutomation_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMAMERCHANT_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAutomation_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMAMERCHANT_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeAutomation_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZEAUTOMAMERCHANT_15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acquirer Code</t>
   </si>
   <si>
@@ -352,33 +387,6 @@
   </si>
   <si>
     <t xml:space="preserve">onlineRefundEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ConfigMerchant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOACONFIGMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIRTELULB_540943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GWMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GWMCCONFIGMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BHOPALMUNICIPALFDC</t>
   </si>
 </sst>
 </file>
@@ -474,7 +482,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -483,16 +491,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -517,10 +525,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -600,8 +604,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="12.90234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="12.796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -633,19 +637,19 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7204644212</v>
-      </c>
-      <c r="D2" s="4" t="s">
+        <v>6758787866</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7204644212</v>
-      </c>
-      <c r="F2" s="4" t="s">
+        <v>6758787866</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -654,41 +658,185 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6758787867</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6758787867</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>8922188849</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>6758787868</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>8922188849</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E4" s="2" t="n">
+        <v>6758787868</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>6758787869</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6758787869</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6758787860</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6758787860</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>7548597789</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>7548597789</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>7548597790</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7548597790</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>7548597791</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7548597791</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7548597792</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>7548597792</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>7548597793</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>7548597793</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -702,7 +850,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.43359375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -722,398 +870,398 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>27</v>
+      <c r="D2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="A3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>35</v>
+      <c r="D3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>37</v>
+      <c r="D4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="E5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="M9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1127,18 +1275,18 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1152,7 +1300,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.30859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1162,235 +1310,235 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="C2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>60</v>
+      <c r="G2" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="4" t="n">
+      <c r="A3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="C3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="E3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>60</v>
+      <c r="G3" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="4" t="n">
+      <c r="A4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="C4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="E4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>60</v>
+      <c r="G4" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="4" t="n">
+      <c r="A5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="E5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>60</v>
+      <c r="G5" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="4" t="n">
+      <c r="A6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="G7" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="E10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>10786</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>60</v>
+      <c r="G10" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1404,7 +1552,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.30859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1421,164 +1569,164 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="N1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="F2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="n">
+      <c r="J2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="n">
+      <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4" t="n">
+      <c r="J3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1592,7 +1740,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1600,58 +1748,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>102</v>
+      <c r="A2" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>104</v>
+      <c r="A3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>105</v>
+      <c r="A4" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>106</v>
+      <c r="A5" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>107</v>
+      <c r="A6" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>108</v>
+      <c r="A7" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1726,101 +1874,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.21"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="11" t="n">
-        <v>7207207201</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>7207207202</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>7207207203</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>7207207205</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="RemotepaySettings" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="PgDetails" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="ConfigDetails" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -44,93 +45,27 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">EzeAutoSuperUser-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A123457</t>
+    <t xml:space="preserve">VineethB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A123456</t>
   </si>
   <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">EzeAutoSuperUser-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutoSuperUser-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutoSuperUser-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutoSuperUser-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoRemote_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutomationRemote_1</t>
+    <t xml:space="preserve">AutotestuserSwati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch59</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">AutoRemote_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutomationRemote_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoRemote_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutomationRemote_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoRemote_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutomationRemote_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoRemote_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutomationRemote_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutomation_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZEAUTOMAMERCHANT_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutomation_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZEAUTOMAMERCHANT_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutomation_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZEAUTOMAMERCHANT_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutomation_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZEAUTOMAMERCHANT_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeAutomation_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZEAUTOMAMERCHANT_15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Acquirer Code</t>
   </si>
   <si>
@@ -417,6 +352,33 @@
   </si>
   <si>
     <t xml:space="preserve">onlineRefundEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConfigMerchant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOACONFIGMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRTELULB_540943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWMCCONFIGMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHOPALMUNICIPALFDC</t>
   </si>
 </sst>
 </file>
@@ -512,7 +474,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -555,6 +517,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -634,8 +600,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="13.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="12.88671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -663,23 +629,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6758787866</v>
-      </c>
-      <c r="D2" s="2" t="s">
+        <v>9731545096</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6758787866</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>9731545096</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -688,285 +654,41 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6758787867</v>
-      </c>
-      <c r="D3" s="2" t="s">
+        <v>8922188849</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6758787867</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>8922188849</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>6758787868</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>6758787868</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>6758787869</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>6758787869</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>6758787860</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>6758787860</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>6548521146</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>6548521146</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>6548521147</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>6548521147</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>6548521148</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>6548521148</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>6548521149</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>6548521149</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>6548521150</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>6548521150</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>7548597789</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>7548597789</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>7548597790</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>7548597790</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>7548597791</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>7548597791</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>7548597792</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>7548597792</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>7548597793</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>7548597793</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -980,7 +702,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1000,398 +722,398 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1405,18 +1127,18 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1430,7 +1152,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1440,235 +1162,235 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1682,7 +1404,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1700,63 +1422,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>120000000008131</v>
@@ -1768,95 +1490,95 @@
         <v>120000000008131</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -1870,7 +1592,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="12.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1878,58 +1600,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2004,7 +1726,101 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>7207207201</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>7207207202</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>7207207203</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>7207207205</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">VineethB</t>
+    <t xml:space="preserve">Manasa</t>
   </si>
   <si>
     <t xml:space="preserve">Ezetap</t>
@@ -601,7 +601,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="12.88671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.90234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -637,13 +637,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9731545096</v>
+        <v>7204644212</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9731545096</v>
+        <v>7204644212</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>9</v>
@@ -702,7 +702,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1152,7 +1152,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.30859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1404,7 +1404,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.30859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1592,7 +1592,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1740,7 +1740,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.87"/>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -15,10 +15,10 @@
     <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="ConfigDetails" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -389,11 +389,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -414,8 +415,17 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -433,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -446,6 +456,13 @@
       <right style="hair"/>
       <top style="hair"/>
       <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -474,12 +491,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -491,23 +508,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -515,12 +532,8 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -600,16 +613,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="12.9921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="4" style="0" width="12.75"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,61 +642,1106 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>7204644212</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>7204644212</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="2" t="n">
         <v>7202020201</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="2" t="n">
         <v>7202020201</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="4"/>
     </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -693,26 +1751,28 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AA1000"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="15" style="0" width="12.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.74"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
@@ -756,7 +1816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -800,7 +1860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
@@ -844,7 +1904,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
@@ -888,7 +1948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>39</v>
       </c>
@@ -932,7 +1992,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
@@ -976,7 +2036,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>44</v>
       </c>
@@ -1020,7 +2080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
@@ -1064,7 +2124,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>34</v>
       </c>
@@ -1108,32 +2168,1020 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J15" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AA52" s="8"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AA53" s="8"/>
     </row>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
-      <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+      <formula1>AcquisitionDetails!$AA$52</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1143,13 +3191,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G1000"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="2" style="0" width="12.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1172,7 +3221,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>57</v>
       </c>
@@ -1195,7 +3244,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>61</v>
       </c>
@@ -1218,7 +3267,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>62</v>
       </c>
@@ -1241,7 +3290,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>63</v>
       </c>
@@ -1264,7 +3313,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>64</v>
       </c>
@@ -1287,7 +3336,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>65</v>
       </c>
@@ -1310,7 +3359,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>66</v>
       </c>
@@ -1333,7 +3382,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>68</v>
       </c>
@@ -1356,7 +3405,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>70</v>
       </c>
@@ -1379,13 +3428,1003 @@
         <v>60</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1395,24 +4434,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Q1000"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="36.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="18" style="0" width="12.13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>71</v>
       </c>
@@ -1465,7 +4507,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -1514,7 +4556,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -1561,19 +4603,1016 @@
         <v>29</v>
       </c>
     </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1583,14 +5622,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="12.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B1000"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="3" style="0" width="11.88"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>100</v>
       </c>
@@ -1598,7 +5638,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>102</v>
       </c>
@@ -1606,7 +5646,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>103</v>
       </c>
@@ -1614,7 +5654,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>105</v>
       </c>
@@ -1622,7 +5662,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>106</v>
       </c>
@@ -1630,7 +5670,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>107</v>
       </c>
@@ -1638,7 +5678,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>108</v>
       </c>
@@ -1646,82 +5686,1052 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10"/>
-    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="8"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="8"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1732,90 +6742,89 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" s="2" t="n">
         <v>7207207201</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="2" t="n">
         <v>7207207202</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="2" t="n">
         <v>7207207203</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="2" t="n">
         <v>7207207205</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="136">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -66,6 +66,21 @@
   </si>
   <si>
     <t xml:space="preserve">EzeAutoSuperUser-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserOne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserTwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserThree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserFour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUserFive</t>
   </si>
   <si>
     <t xml:space="preserve">AutoRemote_1</t>
@@ -634,8 +649,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="13.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="13.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -768,199 +783,299 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6548521146</v>
+        <v>8758787876</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6548521146</v>
+        <v>8758787876</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6548521147</v>
+        <v>8758787877</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>6548521147</v>
+        <v>8758787877</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6548521148</v>
+        <v>8758787878</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6548521148</v>
+        <v>8758787878</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6548521149</v>
+        <v>8758787879</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>6548521149</v>
+        <v>8758787879</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6548521150</v>
+        <v>8758787870</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6548521150</v>
+        <v>8758787870</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>7548597789</v>
+        <v>6548521146</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7548597789</v>
+        <v>6548521146</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>7548597790</v>
+        <v>6548521147</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7548597790</v>
+        <v>6548521147</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>7548597791</v>
+        <v>6548521148</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7548597791</v>
+        <v>6548521148</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>7548597792</v>
+        <v>6548521149</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7548597792</v>
+        <v>6548521149</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>7548597793</v>
+        <v>6548521150</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>6548521150</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>7548597789</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7548597789</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>7548597790</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7548597790</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>7548597791</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7548597791</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>7548597792</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>7548597792</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>7548597793</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>16</v>
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7548597793</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +1095,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -1000,398 +1115,398 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="N4" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="L9" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1430,7 +1545,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1440,229 +1555,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>10786</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1682,7 +1797,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1700,63 +1815,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>120000000008131</v>
@@ -1768,83 +1883,83 @@
         <v>120000000008131</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="n">
         <v>-1</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1985,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="12.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1878,58 +1993,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="119">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -45,40 +45,28 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto-test-user99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch47</t>
+    <t xml:space="preserve">Manasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urvi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARDAUTOMATION_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a123456</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-test-user100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-test-user-98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_eze_user3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_eze_user4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">Acquirer Code</t>
@@ -498,16 +486,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -615,8 +603,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="13.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="13.13671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.92"/>
@@ -644,189 +632,53 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8922133338</v>
-      </c>
-      <c r="D2" s="3" t="s">
+        <v>7204644212</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8922133338</v>
-      </c>
-      <c r="F2" s="3" t="s">
+        <v>7204644212</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8922133339</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
+        <v>7202020201</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8922133339</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>8922133337</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>8922133337</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>7202020201</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>9568426007</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>9568426007</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9568426008</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>9568426008</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>9660867344</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -845,7 +697,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.45"/>
@@ -865,398 +717,398 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="5" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="B2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="I2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="K2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="N3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="6" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="M8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="M9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="6" t="s">
+      <c r="N9" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1295,7 +1147,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.59"/>
   </cols>
@@ -1305,229 +1157,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="5" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="B2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F2" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G5" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="B7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="G7" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="B8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="E10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>10786</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>65</v>
+      <c r="G10" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1547,7 +1399,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="12.40625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.44"/>
@@ -1564,152 +1416,152 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="N1" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="C2" s="4" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>120000000008131</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="I2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>120000000008131</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>120000000008131</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>120000000008131</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="L2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3" t="n">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3" t="n">
-        <v>-1</v>
-      </c>
       <c r="Q3" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1587,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="12.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.25390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.74"/>
@@ -1743,58 +1595,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="5" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B4" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B5" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B6" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="B7" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1883,7 +1735,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.87"/>
@@ -1892,7 +1744,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1905,11 +1757,11 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>115</v>
+      <c r="A2" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>7207207201</v>
@@ -1919,11 +1771,11 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>117</v>
+      <c r="A3" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>7207207202</v>
@@ -1933,11 +1785,11 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>119</v>
+      <c r="A4" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>7207207203</v>
@@ -1947,11 +1799,11 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>121</v>
+      <c r="A5" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>7207207205</v>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="124">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -46,7 +46,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTOTESTMERCHANT8</t>
+    <t xml:space="preserve">AutoTestuserr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto_test_merch57</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -55,12 +58,15 @@
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">Vineeth</t>
+    <t xml:space="preserve">SuperUserFive</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
   </si>
   <si>
+    <t xml:space="preserve">A123458</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
@@ -386,6 +392,9 @@
   </si>
   <si>
     <t xml:space="preserve">PRITHI_203128720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A119000</t>
   </si>
   <si>
     <t xml:space="preserve">Portal_SWA</t>
@@ -484,7 +493,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -495,10 +504,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -615,7 +620,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z4"/>
-  <sheetFormatPr defaultColWidth="14.75" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.92"/>
@@ -644,72 +649,72 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>5555432100</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="C2" s="3" t="n">
+        <v>8922188847</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
+      <c r="E2" s="3" t="n">
+        <v>8922188847</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>8891960880</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8758787870</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -728,7 +733,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="14.37109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.45"/>
@@ -747,407 +752,407 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="M1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="7" t="n">
+      <c r="A2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="8" t="s">
+      <c r="D2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="G2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="E3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="L9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="N9" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AA52" s="10"/>
+      <c r="AA52" s="9"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AA53" s="10"/>
+      <c r="AA53" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1176,239 +1181,239 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="14.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>55</v>
       </c>
+      <c r="F1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="7" t="n">
+      <c r="A2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="7" t="n">
+      <c r="C2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="E2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="6" t="n">
         <v>10786</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="D3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="F3" s="6" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="7" t="n">
+      <c r="C4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="C5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>10786</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G5" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="7" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="E7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>10786</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G7" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="D8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>10786</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="G8" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="E10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>10786</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>59</v>
+      <c r="G10" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1428,7 +1433,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="14.12109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.44"/>
@@ -1445,152 +1450,152 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="B1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>85</v>
       </c>
+      <c r="P1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="7" t="n">
+      <c r="A2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="6" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" s="6" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="G2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7" t="n">
+      <c r="K2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7" t="n">
+      <c r="M3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>28</v>
+      <c r="Q3" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1616,136 +1621,136 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="13.8125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>100</v>
+      <c r="A1" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>66</v>
+      <c r="A2" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>103</v>
+      <c r="A3" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>66</v>
+      <c r="A4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>66</v>
+      <c r="A5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>66</v>
+      <c r="A6" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>66</v>
+      <c r="A7" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10"/>
+      <c r="B8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10"/>
+      <c r="B9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10"/>
+      <c r="B10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10"/>
+      <c r="B11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
+      <c r="B12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10"/>
+      <c r="B13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10"/>
+      <c r="B14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10"/>
+      <c r="B15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10"/>
+      <c r="B16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10"/>
+      <c r="B17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10"/>
+      <c r="B18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10"/>
+      <c r="B19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
+      <c r="B21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10"/>
+      <c r="B22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10"/>
+      <c r="B23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10"/>
+      <c r="B24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10"/>
+      <c r="B25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10"/>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10"/>
+      <c r="B27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10"/>
+      <c r="B28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10"/>
+      <c r="B29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10"/>
+      <c r="B30" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1764,7 +1769,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="13.43359375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.87"/>
@@ -1773,7 +1778,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1786,59 +1791,59 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="12" t="n">
+      <c r="A2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="11" t="n">
         <v>7207207201</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>7</v>
+      <c r="D2" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="12" t="n">
+      <c r="A3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="11" t="n">
         <v>7207207202</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>7</v>
+      <c r="D3" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="12" t="n">
+      <c r="A4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="11" t="n">
         <v>7207207203</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>7</v>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="12" t="n">
+      <c r="A5" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="11" t="n">
         <v>7207207205</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>7</v>
+      <c r="D5" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1863,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.89"/>
@@ -1866,7 +1871,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1879,31 +1884,31 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="A2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>7383838389</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
+      <c r="D2" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="n">
+      <c r="A3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>9886592527</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="129">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -46,28 +46,31 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AutoTestuserr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto_test_merch57</t>
+    <t xml:space="preserve">AVI-EULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
   </si>
   <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTIACCOUNTTESTMERCHANT1</t>
+  </si>
+  <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">SuperUserFive</t>
+    <t xml:space="preserve">test_eze_user3</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
   </si>
   <si>
-    <t xml:space="preserve">A123458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
+    <t xml:space="preserve">test_eze_user4</t>
   </si>
   <si>
     <t xml:space="preserve">Acquirer Code</t>
@@ -112,6 +115,12 @@
     <t xml:space="preserve">Enc Key for UPI</t>
   </si>
   <si>
+    <t xml:space="preserve">Account Label 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Label 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">HDFC</t>
   </si>
   <si>
@@ -121,16 +130,22 @@
     <t xml:space="preserve">True</t>
   </si>
   <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">57c3f7c3b0d8dc0be189ec63f68fce42</t>
   </si>
   <si>
-    <t xml:space="preserve">False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
+    <t xml:space="preserve">acc1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acc2</t>
   </si>
   <si>
     <t xml:space="preserve">AXIS</t>
@@ -358,6 +373,9 @@
     <t xml:space="preserve">onlineRefundEnabled</t>
   </si>
   <si>
+    <t xml:space="preserve">defaultAccount</t>
+  </si>
+  <si>
     <t xml:space="preserve">ConfigMerchant</t>
   </si>
   <si>
@@ -392,9 +410,6 @@
   </si>
   <si>
     <t xml:space="preserve">PRITHI_203128720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A119000</t>
   </si>
   <si>
     <t xml:space="preserve">Portal_SWA</t>
@@ -438,7 +453,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,6 +464,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDEE6EF"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -493,7 +514,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -510,7 +531,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -526,10 +555,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -540,6 +565,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -619,8 +648,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
-  <sheetFormatPr defaultColWidth="14.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.92"/>
@@ -652,69 +681,102 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>8922188847</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>8922188847</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="4" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>9872342331</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9872342331</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="0"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>8758787870</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="C4" s="4" t="n">
+        <v>9568426007</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>9568426007</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>9568426008</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>9568426008</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>9660867345</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -733,7 +795,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="14.515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.45"/>
@@ -747,412 +809,466 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="19.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="18.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="17.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="M1" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="N1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="6" t="n">
+      <c r="A2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="6" t="s">
+      <c r="D2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="F2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="E3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="I7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="J8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="K9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="M9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="O9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="P9" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AA52" s="9"/>
+      <c r="AA52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AA53" s="9"/>
+      <c r="AA53" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1181,239 +1297,239 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="14.265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>57</v>
       </c>
+      <c r="C1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="6" t="n">
+      <c r="A2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="6" t="n">
+      <c r="C2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="8" t="n">
         <v>10786</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>61</v>
+      <c r="G2" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="6" t="n">
+      <c r="A3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="6" t="n">
+      <c r="C3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="6" t="n">
+      <c r="E3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="8" t="n">
         <v>10786</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>61</v>
+      <c r="G3" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="C4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="E4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>10786</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>61</v>
+      <c r="G4" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>10786</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>61</v>
+      <c r="G5" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="F6" s="8" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>10786</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="G7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="6" t="n">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>10786</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>10786</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>10786</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>61</v>
+      <c r="G10" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +1549,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="14.265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.44"/>
@@ -1450,152 +1566,152 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="B1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>87</v>
       </c>
+      <c r="M1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="6" t="n">
+      <c r="A2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="8" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I2" s="6" t="n">
+      <c r="F2" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6" t="n">
+      <c r="J2" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" s="7" t="s">
-        <v>30</v>
+      <c r="Q2" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="K3" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="L3" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6" t="n">
+      <c r="M3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>30</v>
+      <c r="Q3" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1621,136 +1737,141 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="13.95703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.1484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>102</v>
+      <c r="A1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>68</v>
+      <c r="A2" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>105</v>
+      <c r="A3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>68</v>
+      <c r="A4" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>68</v>
+      <c r="A5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>68</v>
+      <c r="A6" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>68</v>
+      <c r="A7" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="9"/>
+      <c r="A8" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9"/>
+      <c r="B9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9"/>
+      <c r="B10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9"/>
+      <c r="B11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9"/>
+      <c r="B12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9"/>
+      <c r="B13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9"/>
+      <c r="B14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9"/>
+      <c r="B15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9"/>
+      <c r="B16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9"/>
+      <c r="B17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9"/>
+      <c r="B18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="9"/>
+      <c r="B19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9"/>
+      <c r="B20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9"/>
+      <c r="B21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="9"/>
+      <c r="B22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="9"/>
+      <c r="B23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9"/>
+      <c r="B24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="9"/>
+      <c r="B25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="9"/>
+      <c r="B26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="9"/>
+      <c r="B27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="9"/>
+      <c r="B28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="9"/>
+      <c r="B29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="9"/>
+      <c r="B30" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1769,7 +1890,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="13.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.76953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.87"/>
@@ -1778,7 +1899,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1791,58 +1912,58 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="11" t="n">
+      <c r="A2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="12" t="n">
         <v>7207207201</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="11" t="n">
+      <c r="A3" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="12" t="n">
         <v>7207207202</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="11" t="n">
+      <c r="A4" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="12" t="n">
         <v>7207207203</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="11" t="n">
+      <c r="A5" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <v>7207207205</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1863,15 +1984,15 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="13" width="17.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="18.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1885,29 +2006,29 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7383838389</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>122</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="A3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="13" t="n">
         <v>9886592527</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="13" t="s">
         <v>8</v>
       </c>
     </row>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="130">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">MULTIACCOUNTTESTMERCHANT1</t>
+    <t xml:space="preserve">TESTMERCHFEBONE02</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t xml:space="preserve">defaultAccount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qrCodePaymentEnabled</t>
   </si>
   <si>
     <t xml:space="preserve">ConfigMerchant</t>
@@ -423,7 +426,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -451,6 +454,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -514,7 +522,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -537,6 +545,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -649,7 +661,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.92"/>
@@ -701,19 +713,19 @@
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9872342331</v>
+        <v>2223442331</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>9872342331</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="6" t="n">
+        <v>2223442331</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="0"/>
@@ -795,7 +807,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="15.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.84765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.45"/>
@@ -814,46 +826,46 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>28</v>
       </c>
       <c r="O1" s="5" t="s">
@@ -864,46 +876,46 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>37</v>
       </c>
       <c r="O2" s="5" t="s">
@@ -914,46 +926,46 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>34</v>
       </c>
       <c r="O3" s="5" t="s">
@@ -964,46 +976,46 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>34</v>
       </c>
       <c r="O4" s="5" t="s">
@@ -1014,46 +1026,46 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="9" t="s">
         <v>34</v>
       </c>
       <c r="O5" s="5" t="s">
@@ -1064,46 +1076,46 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="O6" s="5" t="s">
@@ -1114,46 +1126,46 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>50</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="9" t="s">
         <v>34</v>
       </c>
       <c r="O7" s="5" t="s">
@@ -1164,46 +1176,46 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="9" t="s">
         <v>56</v>
       </c>
       <c r="O8" s="5" t="s">
@@ -1214,46 +1226,46 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="9" t="s">
         <v>34</v>
       </c>
       <c r="O9" s="5" t="s">
@@ -1265,10 +1277,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AA52" s="10"/>
+      <c r="AA52" s="11"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AA53" s="10"/>
+      <c r="AA53" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1297,238 +1309,238 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="15.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="9" t="n">
         <v>10786</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1549,7 +1561,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="15.453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.44"/>
@@ -1558,7 +1570,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="49.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="36.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.77"/>
@@ -1566,151 +1578,151 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="9" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="9" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="9" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="9" t="n">
         <v>120000000008131</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8" t="n">
+      <c r="O2" s="9"/>
+      <c r="P2" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8" t="n">
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8" t="n">
+      <c r="O3" s="9"/>
+      <c r="P3" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1737,65 +1749,65 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="15.1484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1803,75 +1815,80 @@
       <c r="A8" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10"/>
+      <c r="A9" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10"/>
+      <c r="B10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10"/>
+      <c r="B11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
+      <c r="B12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10"/>
+      <c r="B13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10"/>
+      <c r="B14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10"/>
+      <c r="B15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10"/>
+      <c r="B16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10"/>
+      <c r="B17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10"/>
+      <c r="B18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10"/>
+      <c r="B19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10"/>
+      <c r="B20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10"/>
+      <c r="B21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10"/>
+      <c r="B22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10"/>
+      <c r="B23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10"/>
+      <c r="B24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10"/>
+      <c r="B25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10"/>
+      <c r="B26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10"/>
+      <c r="B27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10"/>
+      <c r="B28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10"/>
+      <c r="B29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10"/>
+      <c r="B30" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1890,7 +1907,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="14.76953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.87"/>
@@ -1899,7 +1916,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1912,58 +1929,58 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="B2" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="13" t="n">
         <v>7207207201</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="B3" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="13" t="n">
         <v>7207207202</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="B4" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="13" t="n">
         <v>7207207203</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="B5" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="13" t="n">
         <v>7207207205</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1984,15 +2001,15 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="13.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.3984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="13" width="17.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="18.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="14" width="17.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="18.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -2006,10 +2023,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7383838389</v>
@@ -2019,16 +2036,16 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="14" t="n">
         <v>9886592527</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>8</v>
       </c>
     </row>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="164">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -46,10 +46,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">AVI-EULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap</t>
+    <t xml:space="preserve">SuperUsr_multiAcc_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_1</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -58,364 +58,466 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">TESTMERCHFEBONE02</t>
+    <t xml:space="preserve">SuperUsr_multiAcc_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperUsr_multiAcc_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperEzeUsrMultiAcc_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_1</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">test_eze_user3</t>
+    <t xml:space="preserve">ChildUser_multiAcc_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildUser_multiAcc_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChildEzeUserMultiAcc_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquirer Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Terminals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSM Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI(psp) Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App Key for UPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">virtual MID Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BQR settings required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPI settings required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enc Key for UPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Label 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Label 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57c3f7c3b0d8dc0be189ec63f68fce42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acc1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acc2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS_DIRECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC_ICICI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATOS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXIS_TLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_ATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOTAK_WL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4ba841d6-c012-4d19-ab49-2ee74366171p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7f617238-fb82-4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EntityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cnpTxnTimeoutDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_binary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maximumPayAttemptsAllowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxUpiAttemptInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePayExpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rmpayBumpTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnAndroidDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiCollectEnableOnNonAndroidDevices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabledInCNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Api Key3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hash Algo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mle Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb Selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cnp Cardpay Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account Label Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNP Terminal Dependant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYBERSOURCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DV+y0pRK1jhkpBipZ+YtM06XqQGOi1SDwsmOY/K4wqo=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8bf3bb8f-eb7c-45d2-b227-bf779907d017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2989436385NXGVOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4053377546CSKYIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T297100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIRST_amount_0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470|TPSL Bank::</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upiEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qrCodesEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHARAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remotePaymentEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ctlsEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refundEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onlineRefundEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defaultAccount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ConfigMerchant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOACONFIGMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRTELULB_540943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWMCCONFIGMERCHANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHOPALMUNICIPALFDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenericMerchant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRITHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRITHI_203128720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal_SWA</t>
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_eze_user4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acquirer Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payment Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Terminals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSM Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BQR Bank Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPI(psp) Bank Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BQR Terminal Dependant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPI Terminal Dependant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App Key for UPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">virtual MID Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BQR settings required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPI settings required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enc Key for UPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account Label 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account Label 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDFC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57c3f7c3b0d8dc0be189ec63f68fce42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acc1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acc2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXIS_DIRECT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICICI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDC_ICICI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATOS_TLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AXIS_TLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOTAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOTAK_ATOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOTAK_WL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4ba841d6-c012-4d19-ab49-2ee74366171p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7f617238-fb82-4b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LockId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EntityId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inheritable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cnpTxnTimeoutDuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_binary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maximumPayAttemptsAllowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maxUpiAttemptInCNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remotePayExpTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rmpayBumpCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rmpayBumpTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upiCollectEnableOnAndroidDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upiCollectEnableOnNonAndroidDevices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upiEnabledInCNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Api Key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secret</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Api Key2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secret2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Api Key3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secret3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lock Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hash Algo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mle Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nb Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nb Selected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cnp Cardpay Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account Label Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transaction Timeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNP Terminal Dependant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYBERSOURCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DV+y0pRK1jhkpBipZ+YtM06XqQGOi1SDwsmOY/K4wqo=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8bf3bb8f-eb7c-45d2-b227-bf779907d017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ezetap_2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INACTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPSL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2989436385NXGVOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4053377546CSKYIV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T297100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIRST_amount_0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470|TPSL Bank::</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setting Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Setting Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upiEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qrCodesEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BHARAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remotePaymentEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ctlsEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refundEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onlineRefundEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defaultAccount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qrCodePaymentEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ConfigMerchant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOACONFIGMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIRTELULB_540943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GWMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GWMCCONFIGMERCHANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BHOPALMUNICIPALFDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenericMerchant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRITHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRITHI_203128720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal_SWA</t>
   </si>
 </sst>
 </file>
@@ -426,7 +528,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -455,13 +557,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -474,14 +571,8 @@
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -494,6 +585,13 @@
       <right style="hair"/>
       <top style="hair"/>
       <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -547,11 +645,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -660,8 +758,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="16.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="16.18359375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.92"/>
@@ -693,17 +791,17 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>9660867345</v>
+        <v>5647396758</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>9660867345</v>
+        <v>5647396758</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
@@ -713,58 +811,58 @@
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>2223442331</v>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>9089086784</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="n">
-        <v>2223442331</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>11</v>
+      <c r="E3" s="4" t="n">
+        <v>9089086784</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="G3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9568426007</v>
+        <v>1233212375</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9568426007</v>
+        <v>1233212375</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>13</v>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9568426008</v>
+        <v>5644345456</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>9568426008</v>
+        <v>5644345456</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>9</v>
@@ -772,22 +870,322 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9660867345</v>
+        <v>6758493874</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9660867345</v>
+        <v>6758493874</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5743975326</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5743975326</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>7455424326</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>7455424326</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>7865635478</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>7865635478</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>9885964604</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>9885964604</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>9764957305</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>9764957305</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>9090476985</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>9090476985</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>9867656790</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9867656790</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>7945830054</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>7945830054</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>8767489056</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>8767489056</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>6394564500</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>6394564500</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>7976979594</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>7976979594</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>9237458843</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9237458843</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>2394564597</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>2394564597</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>9785649674</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>9785649674</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>9794649343</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>9794649343</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -807,7 +1205,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="15.84765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.45"/>
@@ -827,452 +1225,452 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1309,7 +1707,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="15.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.59"/>
   </cols>
@@ -1319,229 +1717,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="B3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1561,7 +1959,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="15.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.44"/>
@@ -1579,63 +1977,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>120000000008131</v>
@@ -1647,83 +2045,83 @@
         <v>120000000008131</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="I2" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +2147,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="15.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.21875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.74"/>
@@ -1757,75 +2155,70 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>73</v>
-      </c>
+      <c r="B9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11"/>
@@ -1907,7 +2300,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="14.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.87"/>
@@ -1916,7 +2309,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1930,10 +2323,10 @@
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>7207207201</v>
@@ -1944,10 +2337,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>7207207202</v>
@@ -1958,10 +2351,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>7207207203</v>
@@ -1972,10 +2365,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>7207207205</v>
@@ -2001,7 +2394,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="13.3984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.34375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="14" width="17.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="18.89"/>
@@ -2009,7 +2402,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -2023,10 +2416,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7383838389</v>
@@ -2037,10 +2430,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="C3" s="14" t="n">
         <v>9886592527</v>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="165">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -112,67 +112,67 @@
     <t xml:space="preserve">SuperEzeUsrMultiAcc_10</t>
   </si>
   <si>
-    <t xml:space="preserve">ChildUser_multiAcc_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_1</t>
+    <t xml:space="preserve">User_multiAcc_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_1</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">ChildUser_multiAcc_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildUser_multiAcc_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChildEzeUserMultiAcc_10</t>
+    <t xml:space="preserve">User_multiAcc_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User_multiAcc_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EzeUserMultiAcc_10</t>
   </si>
   <si>
     <t xml:space="preserve">Acquirer Code</t>
@@ -476,6 +476,9 @@
   </si>
   <si>
     <t xml:space="preserve">defaultAccount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qrCodePaymentEnabled</t>
   </si>
   <si>
     <t xml:space="preserve">ConfigMerchant</t>
@@ -759,7 +762,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="16.18359375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.92"/>
@@ -996,13 +999,13 @@
         <v>29</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>9090476985</v>
+        <v>9465798343</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>9090476985</v>
+        <v>9465798343</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>30</v>
@@ -1016,13 +1019,13 @@
         <v>32</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>9867656790</v>
+        <v>4359673632</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9867656790</v>
+        <v>4359673632</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>30</v>
@@ -1036,13 +1039,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>7945830054</v>
+        <v>2345523255</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7945830054</v>
+        <v>2345523255</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>30</v>
@@ -1056,13 +1059,13 @@
         <v>36</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>8767489056</v>
+        <v>1244586776</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>8767489056</v>
+        <v>1244586776</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>30</v>
@@ -1076,13 +1079,13 @@
         <v>38</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>6394564500</v>
+        <v>7353623522</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>6394564500</v>
+        <v>7353623522</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>30</v>
@@ -1096,13 +1099,13 @@
         <v>40</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>7976979594</v>
+        <v>2255652454</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>7976979594</v>
+        <v>2255652454</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>30</v>
@@ -1116,13 +1119,13 @@
         <v>42</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>9237458843</v>
+        <v>3352457345</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>9237458843</v>
+        <v>3352457345</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>30</v>
@@ -1136,13 +1139,13 @@
         <v>44</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>2394564597</v>
+        <v>3572745624</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>2394564597</v>
+        <v>3572745624</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>30</v>
@@ -1156,13 +1159,13 @@
         <v>46</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>9785649674</v>
+        <v>7456456235</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>9785649674</v>
+        <v>7456456235</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>30</v>
@@ -1176,13 +1179,13 @@
         <v>48</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>9794649343</v>
+        <v>8657544353</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>9794649343</v>
+        <v>8657544353</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>30</v>
@@ -1191,7 +1194,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -1205,7 +1208,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="15.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.8671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.45"/>
@@ -1682,18 +1685,18 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -1707,7 +1710,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="15.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.59765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.59"/>
   </cols>
@@ -1945,7 +1948,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -1959,7 +1962,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="15.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.59765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.44"/>
@@ -2126,14 +2129,14 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -2147,7 +2150,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="15.21875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.74"/>
@@ -2218,7 +2221,12 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11"/>
+      <c r="A9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11"/>
@@ -2286,7 +2294,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -2300,7 +2308,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="14.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.87"/>
@@ -2309,7 +2317,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -2323,10 +2331,10 @@
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>7207207201</v>
@@ -2337,10 +2345,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>7207207202</v>
@@ -2351,10 +2359,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>7207207203</v>
@@ -2365,10 +2373,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>7207207205</v>
@@ -2380,7 +2388,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -2394,7 +2402,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="13.34375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.41796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="14" width="17.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="18.89"/>
@@ -2402,7 +2410,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -2416,10 +2424,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7383838389</v>
@@ -2430,10 +2438,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" s="14" t="n">
         <v>9886592527</v>
@@ -2445,7 +2453,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/DataProvider/merchant_user_creation.xlsx
+++ b/DataProvider/merchant_user_creation.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="UserDetails" sheetId="1" state="visible" r:id="rId2"/>
@@ -15,6 +15,7 @@
     <sheet name="OrgSettings" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="ConfigDetails" sheetId="6" state="visible" r:id="rId7"/>
     <sheet name="Generic" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="EzeGro" sheetId="8" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="137">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -46,10 +47,10 @@
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_1</t>
+    <t xml:space="preserve">Manasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezetap</t>
   </si>
   <si>
     <t xml:space="preserve">A123456</t>
@@ -58,123 +59,15 @@
     <t xml:space="preserve">Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperUsr_multiAcc_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperEzeUsrMultiAcc_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_1</t>
+    <t xml:space="preserve">Vinay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISAUTOMATION_908</t>
   </si>
   <si>
     <t xml:space="preserve">App</t>
   </si>
   <si>
-    <t xml:space="preserve">User_multiAcc_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User_multiAcc_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EzeUserMultiAcc_10</t>
-  </si>
-  <si>
     <t xml:space="preserve">Acquirer Code</t>
   </si>
   <si>
@@ -521,6 +414,30 @@
   </si>
   <si>
     <t xml:space="preserve">EZETAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UserType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MobileNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApplicationKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeviceIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeviceIdentifierType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ezegrow_user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e32af812-9127-4c82-824e-105458370eaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imei</t>
   </si>
 </sst>
 </file>
@@ -531,7 +448,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -558,6 +475,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF067D17"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -623,7 +547,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -640,12 +564,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -684,6 +608,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,7 +632,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF067D17"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -761,8 +689,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="16.265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="16.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.92"/>
@@ -797,16 +725,16 @@
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>5647396758</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="3" t="n">
+        <v>7204644212</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>5647396758</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="3" t="n">
+        <v>7204644212</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -817,384 +745,176 @@
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>9089086784</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="3" t="n">
+        <v>7207207205</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>9089086784</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="0"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="E3" s="3" t="n">
+        <v>7207207205</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1233212375</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1233212375</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>5644345456</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>5644345456</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6758493874</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>6758493874</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>5743975326</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>5743975326</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>7455424326</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>7455424326</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>7865635478</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>7865635478</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>9885964604</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>9885964604</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>9764957305</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>9764957305</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>9465798343</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>9465798343</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>4359673632</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>4359673632</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>2345523255</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>2345523255</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>1244586776</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1244586776</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>7353623522</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>7353623522</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>2255652454</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>2255652454</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>3352457345</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>3352457345</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>3572745624</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>3572745624</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>7456456235</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>7456456235</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>8657544353</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>8657544353</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -1208,7 +928,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA53"/>
-  <sheetFormatPr defaultColWidth="15.8671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.3984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.45"/>
@@ -1228,452 +948,452 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>64</v>
+        <v>26</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>73</v>
+        <v>35</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>86</v>
+        <v>48</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>73</v>
+        <v>54</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1685,18 +1405,18 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K2:K9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$52</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:I9" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -1710,7 +1430,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="15.59765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.12890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.59"/>
   </cols>
@@ -1720,235 +1440,235 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="B3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>10786</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -1962,7 +1682,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultColWidth="15.59765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="16.12890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.44"/>
@@ -1971,7 +1691,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="49.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="36.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.9"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.77"/>
@@ -1980,63 +1700,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>120000000008131</v>
@@ -2048,95 +1768,95 @@
         <v>120000000008131</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="I2" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9" t="n">
         <v>-1</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
+    <dataValidation allowBlank="true" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q2:Q3" type="list">
       <formula1>AcquisitionDetails!$AA$52:$AA$53</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -2150,7 +1870,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="15.2890625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.8046875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.74"/>
@@ -2158,74 +1878,74 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>149</v>
+      <c r="A8" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2294,7 +2014,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -2308,7 +2028,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="14.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="15.41796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.87"/>
@@ -2317,7 +2037,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -2331,10 +2051,10 @@
     </row>
     <row r="2" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>7207207201</v>
@@ -2345,10 +2065,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>7207207202</v>
@@ -2359,10 +2079,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>7207207203</v>
@@ -2373,10 +2093,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>7207207205</v>
@@ -2388,7 +2108,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
@@ -2402,7 +2122,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="13.41796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="14" width="17.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="18.89"/>
@@ -2410,7 +2130,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -2424,10 +2144,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7383838389</v>
@@ -2438,10 +2158,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C3" s="14" t="n">
         <v>9886592527</v>
@@ -2453,7 +2173,83 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth=